--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -795,12 +795,7 @@
         <v>81368550</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420859.7601243296</v>
+        <v>420860</v>
       </c>
       <c r="R3" t="n">
-        <v>6190239.832464891</v>
+        <v>6190240</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +860,9 @@
           <t>2014-07-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>81368550</v>
       </c>
       <c r="B3" t="n">
-        <v>98692</v>
+        <v>98696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>81368550</v>
       </c>
       <c r="B3" t="n">
-        <v>98696</v>
+        <v>98698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>81368550</v>
       </c>
       <c r="B3" t="n">
-        <v>98698</v>
+        <v>98708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>81368550</v>
       </c>
       <c r="B3" t="n">
-        <v>98708</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>81368550</v>
       </c>
       <c r="B3" t="n">
-        <v>98749</v>
+        <v>98751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39855-2022 artfynd.xlsx
+++ b/artfynd/A 39855-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81368525</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81368358</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80923932</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81368477</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,8 +1224,20 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81368550</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>